--- a/data/trans_orig/P41D_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Edad-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>799</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8930</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
